--- a/Step2/Outputs/Behavioural_comparison.xlsx
+++ b/Step2/Outputs/Behavioural_comparison.xlsx
@@ -538,19 +538,19 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>41.99770837201868</v>
+        <v>41.99770820227786</v>
       </c>
       <c r="D4">
-        <v>150.9907412600151</v>
+        <v>150.9907406383718</v>
       </c>
       <c r="E4">
-        <v>249.9851853000036</v>
+        <v>249.9851842755379</v>
       </c>
       <c r="F4">
-        <v>367.9760512899993</v>
+        <v>367.9760498750074</v>
       </c>
       <c r="G4">
-        <v>589.9614745900071</v>
+        <v>589.9614723245322</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -559,19 +559,19 @@
         <v>15</v>
       </c>
       <c r="L4">
-        <v>6.599995404030778</v>
+        <v>6.599995306743949</v>
       </c>
       <c r="M4">
-        <v>32.00171394999779</v>
+        <v>32.00171362909896</v>
       </c>
       <c r="N4">
-        <v>76.00006672002201</v>
+        <v>76.00006599493645</v>
       </c>
       <c r="O4">
-        <v>127.9981991900204</v>
+        <v>127.9981981845122</v>
       </c>
       <c r="P4">
-        <v>285.9928224700343</v>
+        <v>285.9928205178294</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -580,19 +580,19 @@
         <v>16</v>
       </c>
       <c r="U4">
-        <v>-33.59777936398314</v>
+        <v>-33.59777916091844</v>
       </c>
       <c r="V4">
-        <v>-147.9926861600106</v>
+        <v>-147.9926853840734</v>
       </c>
       <c r="W4">
-        <v>-260.9870099700056</v>
+        <v>-260.9870086445917</v>
       </c>
       <c r="X4">
-        <v>-390.9797043199942</v>
+        <v>-390.9797024023683</v>
       </c>
       <c r="Y4">
-        <v>-694.9633522099793</v>
+        <v>-694.9633488041291</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -601,19 +601,19 @@
         <v>17</v>
       </c>
       <c r="AD4">
-        <v>-12.59993085000042</v>
+        <v>-12.59993078543448</v>
       </c>
       <c r="AE4">
-        <v>-33.99825557000258</v>
+        <v>-33.99825538116056</v>
       </c>
       <c r="AF4">
-        <v>-61.99802105999879</v>
+        <v>-61.99802078155972</v>
       </c>
       <c r="AG4">
-        <v>-101.9946525300038</v>
+        <v>-101.9946520041976</v>
       </c>
       <c r="AH4">
-        <v>-183.9909384900002</v>
+        <v>-183.9909376030646</v>
       </c>
       <c r="AK4">
         <v>10</v>
@@ -643,7 +643,7 @@
         <v>12</v>
       </c>
       <c r="AV4">
-        <v>1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AW4">
         <v>0</v>
@@ -666,19 +666,19 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>7.559189957998569</v>
+        <v>7.559189889621848</v>
       </c>
       <c r="D5">
-        <v>31.01271532999999</v>
+        <v>31.01271504591114</v>
       </c>
       <c r="E5">
-        <v>49.22555210999963</v>
+        <v>49.22555169315274</v>
       </c>
       <c r="F5">
-        <v>69.61906678000105</v>
+        <v>69.61906621442904</v>
       </c>
       <c r="G5">
-        <v>119.6523952199986</v>
+        <v>119.6523941814057</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -687,19 +687,19 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>14.28271040999971</v>
+        <v>14.28271025558206</v>
       </c>
       <c r="M5">
-        <v>55.41154974999154</v>
+        <v>55.41154908434692</v>
       </c>
       <c r="N5">
-        <v>96.82297362001556</v>
+        <v>96.82297249035037</v>
       </c>
       <c r="O5">
-        <v>140.0487370999981</v>
+        <v>140.0487354428587</v>
       </c>
       <c r="P5">
-        <v>240.467672419989</v>
+        <v>240.4676696416936</v>
       </c>
       <c r="S5">
         <v>2</v>
@@ -708,19 +708,19 @@
         <v>16</v>
       </c>
       <c r="U5">
-        <v>-15.84593359800419</v>
+        <v>-15.84593341790242</v>
       </c>
       <c r="V5">
-        <v>-66.81233756999427</v>
+        <v>-66.81233687077838</v>
       </c>
       <c r="W5">
-        <v>-109.8293238200094</v>
+        <v>-109.8293226908427</v>
       </c>
       <c r="X5">
-        <v>-160.6449036199956</v>
+        <v>-160.6449019511637</v>
       </c>
       <c r="Y5">
-        <v>-273.0689444999953</v>
+        <v>-273.0689417027315</v>
       </c>
       <c r="AB5">
         <v>2</v>
@@ -729,19 +729,19 @@
         <v>17</v>
       </c>
       <c r="AD5">
-        <v>-4.686778049999703</v>
+        <v>-4.686777983735738</v>
       </c>
       <c r="AE5">
-        <v>-16.80258491999757</v>
+        <v>-16.80258474301081</v>
       </c>
       <c r="AF5">
-        <v>-29.41434791999563</v>
+        <v>-29.41434758541618</v>
       </c>
       <c r="AG5">
-        <v>-45.02333463999821</v>
+        <v>-45.02333410104075</v>
       </c>
       <c r="AH5">
-        <v>-82.05810324999584</v>
+        <v>-82.05810224674315</v>
       </c>
       <c r="AK5">
         <v>2</v>
@@ -794,19 +794,19 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>35.99356822801201</v>
+        <v>35.993567968555</v>
       </c>
       <c r="D6">
-        <v>128.9783327900041</v>
+        <v>128.9783318617192</v>
       </c>
       <c r="E6">
-        <v>209.9670790900018</v>
+        <v>209.9670775491686</v>
       </c>
       <c r="F6">
-        <v>311.9452597700038</v>
+        <v>311.9452574173883</v>
       </c>
       <c r="G6">
-        <v>508.9015454100117</v>
+        <v>508.9015414751993</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -815,19 +815,19 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>0.5937070560175925</v>
+        <v>0.5937071499356534</v>
       </c>
       <c r="M6">
-        <v>14.97902229997999</v>
+        <v>14.97902262076968</v>
       </c>
       <c r="N6">
-        <v>41.95773629998439</v>
+        <v>41.95773678777914</v>
       </c>
       <c r="O6">
-        <v>73.94770455999242</v>
+        <v>73.94770521562168</v>
       </c>
       <c r="P6">
-        <v>188.8833148600242</v>
+        <v>188.8833155720131</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -836,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="U6">
-        <v>-28.18718360399908</v>
+        <v>-28.18718350052222</v>
       </c>
       <c r="V6">
-        <v>-117.967918639999</v>
+        <v>-117.967918150578</v>
       </c>
       <c r="W6">
-        <v>-204.9353845299993</v>
+        <v>-204.9353836744085</v>
       </c>
       <c r="X6">
-        <v>-308.9031499599951</v>
+        <v>-308.9031486658314</v>
       </c>
       <c r="Y6">
-        <v>-562.838528329994</v>
+        <v>-562.8385257745103</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -857,19 +857,19 @@
         <v>17</v>
       </c>
       <c r="AD6">
-        <v>-7.793523708000976</v>
+        <v>-7.793523654511773</v>
       </c>
       <c r="AE6">
-        <v>-22.00022939999963</v>
+        <v>-22.00022932710363</v>
       </c>
       <c r="AF6">
-        <v>-47.97848703000182</v>
+        <v>-47.97848681974938</v>
       </c>
       <c r="AG6">
-        <v>-72.97886801999539</v>
+        <v>-72.97886766284682</v>
       </c>
       <c r="AH6">
-        <v>-136.9575837299981</v>
+        <v>-136.9575830404747</v>
       </c>
       <c r="AK6">
         <v>9</v>
@@ -878,7 +878,7 @@
         <v>11</v>
       </c>
       <c r="AM6">
-        <v>-1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AW6">
-        <v>1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AX6">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>1.455191522836685E-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:52">
@@ -922,19 +922,19 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>1.800137046000145</v>
+        <v>1.800137002075644</v>
       </c>
       <c r="D7">
-        <v>6.000567080000565</v>
+        <v>6.000566934378185</v>
       </c>
       <c r="E7">
-        <v>11.00093676000051</v>
+        <v>11.00093655330056</v>
       </c>
       <c r="F7">
-        <v>14.44902399999955</v>
+        <v>14.4490237055229</v>
       </c>
       <c r="G7">
-        <v>22.00238880000006</v>
+        <v>22.00238828927604</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -943,19 +943,19 @@
         <v>15</v>
       </c>
       <c r="L7">
-        <v>3.60002283599988</v>
+        <v>3.600022811598137</v>
       </c>
       <c r="M7">
-        <v>16.8955271800005</v>
+        <v>16.89552705611004</v>
       </c>
       <c r="N7">
-        <v>29.89570900999934</v>
+        <v>29.89570878135964</v>
       </c>
       <c r="O7">
-        <v>39.34374831000059</v>
+        <v>39.3437480044322</v>
       </c>
       <c r="P7">
-        <v>68.23967850999725</v>
+        <v>68.23967795874523</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -964,19 +964,19 @@
         <v>16</v>
       </c>
       <c r="U7">
-        <v>-3.60020256000098</v>
+        <v>-3.600202511033785</v>
       </c>
       <c r="V7">
-        <v>-17.4482016100028</v>
+        <v>-17.44820142414756</v>
       </c>
       <c r="W7">
-        <v>-27.89635855999859</v>
+        <v>-27.89635825792812</v>
       </c>
       <c r="X7">
-        <v>-41.89687413999945</v>
+        <v>-41.8968736765637</v>
       </c>
       <c r="Y7">
-        <v>-69.79352148999988</v>
+        <v>-69.79352071261383</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -985,19 +985,19 @@
         <v>17</v>
       </c>
       <c r="AD7">
-        <v>-1.800068441998974</v>
+        <v>-1.800068416704107</v>
       </c>
       <c r="AE7">
-        <v>-3.447709869999472</v>
+        <v>-3.44770982720911</v>
       </c>
       <c r="AF7">
-        <v>-8.447927919999984</v>
+        <v>-8.44792781448723</v>
       </c>
       <c r="AG7">
-        <v>-12.89582192999978</v>
+        <v>-12.89582178197907</v>
       </c>
       <c r="AH7">
-        <v>-23.89621536000004</v>
+        <v>-23.89621510633515</v>
       </c>
       <c r="AK7">
         <v>7</v>
@@ -1006,7 +1006,7 @@
         <v>11</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AN7">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>-3.637978807091713E-12</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>-3.637978807091713E-12</v>
       </c>
       <c r="AY7">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1050,19 +1050,19 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>6.621567330001199</v>
+        <v>6.62156735617009</v>
       </c>
       <c r="D8">
-        <v>24.00331197000014</v>
+        <v>24.00331202964026</v>
       </c>
       <c r="E8">
-        <v>40.0362664500044</v>
+        <v>40.03626657158293</v>
       </c>
       <c r="F8">
-        <v>59.24375416999737</v>
+        <v>59.24375427729683</v>
       </c>
       <c r="G8">
-        <v>93.11449381999864</v>
+        <v>93.11449404347331</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -1071,19 +1071,19 @@
         <v>15</v>
       </c>
       <c r="L8">
-        <v>8.419319009997707</v>
+        <v>8.419319012158667</v>
       </c>
       <c r="M8">
-        <v>31.2626093900144</v>
+        <v>31.26260937349434</v>
       </c>
       <c r="N8">
-        <v>49.69461906999641</v>
+        <v>49.69461903729098</v>
       </c>
       <c r="O8">
-        <v>75.96015851997799</v>
+        <v>75.96015850529511</v>
       </c>
       <c r="P8">
-        <v>130.2580216600036</v>
+        <v>130.2580216067799</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1092,19 +1092,19 @@
         <v>16</v>
       </c>
       <c r="U8">
-        <v>-11.540573957991</v>
+        <v>-11.54057396552344</v>
       </c>
       <c r="V8">
-        <v>-42.26825541001381</v>
+        <v>-42.26825544990606</v>
       </c>
       <c r="W8">
-        <v>-73.50005186999806</v>
+        <v>-73.50005197351129</v>
       </c>
       <c r="X8">
-        <v>-102.5345394100004</v>
+        <v>-102.5345395360946</v>
       </c>
       <c r="Y8">
-        <v>-173.0378280699933</v>
+        <v>-173.0378283102291</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1113,19 +1113,19 @@
         <v>17</v>
       </c>
       <c r="AD8">
-        <v>-3.019329683997966</v>
+        <v>-3.019329693101099</v>
       </c>
       <c r="AE8">
-        <v>-11.20235163000052</v>
+        <v>-11.20235162000154</v>
       </c>
       <c r="AF8">
-        <v>-19.23495088000254</v>
+        <v>-19.23495089462449</v>
       </c>
       <c r="AG8">
-        <v>-27.26775361000637</v>
+        <v>-27.2677536373094</v>
       </c>
       <c r="AH8">
-        <v>-51.50024051000582</v>
+        <v>-51.50024046685849</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -1178,19 +1178,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>13.79852745600692</v>
+        <v>13.79852746747929</v>
       </c>
       <c r="D9">
-        <v>45.99491747999855</v>
+        <v>45.99491750908601</v>
       </c>
       <c r="E9">
-        <v>76.99216813000021</v>
+        <v>76.99216819736284</v>
       </c>
       <c r="F9">
-        <v>110.9880148100001</v>
+        <v>110.9880149023502</v>
       </c>
       <c r="G9">
-        <v>181.9796894500032</v>
+        <v>181.9796896003918</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1199,19 +1199,19 @@
         <v>15</v>
       </c>
       <c r="L9">
-        <v>8.399033699988649</v>
+        <v>8.399033712681558</v>
       </c>
       <c r="M9">
-        <v>40.99524036999355</v>
+        <v>40.99524043342899</v>
       </c>
       <c r="N9">
-        <v>67.99135879997993</v>
+        <v>67.99135891881087</v>
       </c>
       <c r="O9">
-        <v>106.9876004699981</v>
+        <v>106.9876006380109</v>
       </c>
       <c r="P9">
-        <v>197.976852920001</v>
+        <v>197.9768532053058</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1220,19 +1220,19 @@
         <v>16</v>
       </c>
       <c r="U9">
-        <v>-18.59790190198873</v>
+        <v>-18.59790192498804</v>
       </c>
       <c r="V9">
-        <v>-67.99259770999925</v>
+        <v>-67.99259779317254</v>
       </c>
       <c r="W9">
-        <v>-110.987932289996</v>
+        <v>-110.9879324211634</v>
       </c>
       <c r="X9">
-        <v>-161.9818012700089</v>
+        <v>-161.9818014549674</v>
       </c>
       <c r="Y9">
-        <v>-276.9695907899986</v>
+        <v>-276.9695910882328</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1241,19 +1241,19 @@
         <v>17</v>
       </c>
       <c r="AD9">
-        <v>-5.999288105997948</v>
+        <v>-5.999288110768248</v>
       </c>
       <c r="AE9">
-        <v>-19.99808823999865</v>
+        <v>-19.99808826481149</v>
       </c>
       <c r="AF9">
-        <v>-34.99570851000135</v>
+        <v>-34.9957085765891</v>
       </c>
       <c r="AG9">
-        <v>-57.99327912999888</v>
+        <v>-57.9932792126292</v>
       </c>
       <c r="AH9">
-        <v>-100.9871140200021</v>
+        <v>-100.9871141298745</v>
       </c>
       <c r="AK9">
         <v>5</v>
@@ -1286,13 +1286,13 @@
         <v>0</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>7.275957614183426E-12</v>
       </c>
       <c r="AX9">
         <v>0</v>
       </c>
       <c r="AY9">
-        <v>-7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -1306,19 +1306,19 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>4.806785201999446</v>
+        <v>4.806785208947076</v>
       </c>
       <c r="D10">
-        <v>22.02266215999953</v>
+        <v>22.02266207288358</v>
       </c>
       <c r="E10">
-        <v>37.0338968299975</v>
+        <v>37.03389672690355</v>
       </c>
       <c r="F10">
-        <v>52.05691594999826</v>
+        <v>52.05691581512201</v>
       </c>
       <c r="G10">
-        <v>86.10109676999764</v>
+        <v>86.10109645390457</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1327,19 +1327,19 @@
         <v>15</v>
       </c>
       <c r="L10">
-        <v>11.40655397999944</v>
+        <v>11.4065539247058</v>
       </c>
       <c r="M10">
-        <v>44.02250979999735</v>
+        <v>44.02250959088269</v>
       </c>
       <c r="N10">
-        <v>77.04480126000635</v>
+        <v>77.04480096220504</v>
       </c>
       <c r="O10">
-        <v>116.0555323999943</v>
+        <v>116.0555319120103</v>
       </c>
       <c r="P10">
-        <v>189.1228752399875</v>
+        <v>189.1228743970387</v>
       </c>
       <c r="S10">
         <v>3</v>
@@ -1348,19 +1348,19 @@
         <v>16</v>
       </c>
       <c r="U10">
-        <v>-15.01298298000256</v>
+        <v>-15.01298289787155</v>
       </c>
       <c r="V10">
-        <v>-53.0332904199895</v>
+        <v>-53.03329017409124</v>
       </c>
       <c r="W10">
-        <v>-87.06668509999872</v>
+        <v>-87.06668474826438</v>
       </c>
       <c r="X10">
-        <v>-128.1001220600119</v>
+        <v>-128.1001215316974</v>
       </c>
       <c r="Y10">
-        <v>-206.1677431200042</v>
+        <v>-206.1677422887078</v>
       </c>
       <c r="AB10">
         <v>3</v>
@@ -1369,19 +1369,19 @@
         <v>17</v>
       </c>
       <c r="AD10">
-        <v>-4.806442164001965</v>
+        <v>-4.806442112310833</v>
       </c>
       <c r="AE10">
-        <v>-16.00003079000362</v>
+        <v>-16.00003073036351</v>
       </c>
       <c r="AF10">
-        <v>-25.02232642000399</v>
+        <v>-25.02232631485185</v>
       </c>
       <c r="AG10">
-        <v>-43.02202946000398</v>
+        <v>-43.02202927584858</v>
       </c>
       <c r="AH10">
-        <v>-66.04508402999636</v>
+        <v>-66.04508373720637</v>
       </c>
       <c r="AK10">
         <v>3</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="AW10">
-        <v>7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AX10">
         <v>0</v>
@@ -1434,19 +1434,19 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>4.799997467999219</v>
+        <v>4.799997475412511</v>
       </c>
       <c r="D11">
-        <v>12.99999445999992</v>
+        <v>12.99999443571369</v>
       </c>
       <c r="E11">
-        <v>24.99998953999921</v>
+        <v>24.99998957207936</v>
       </c>
       <c r="F11">
-        <v>32.99998656000025</v>
+        <v>32.99998654723777</v>
       </c>
       <c r="G11">
-        <v>49.99998141999959</v>
+        <v>49.9999814020116</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1455,19 +1455,19 @@
         <v>15</v>
       </c>
       <c r="L11">
-        <v>7.972119852005562</v>
+        <v>7.972119843852852</v>
       </c>
       <c r="M11">
-        <v>32.57372923999174</v>
+        <v>32.57372921532442</v>
       </c>
       <c r="N11">
-        <v>53.5737178000054</v>
+        <v>53.57371778046036</v>
       </c>
       <c r="O11">
-        <v>81.14745027999925</v>
+        <v>81.14745023494652</v>
       </c>
       <c r="P11">
-        <v>135.1474174900013</v>
+        <v>135.1474174442319</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1476,19 +1476,19 @@
         <v>16</v>
       </c>
       <c r="U11">
-        <v>-9.772118940005385</v>
+        <v>-9.772118935750768</v>
       </c>
       <c r="V11">
-        <v>-34.28685545999724</v>
+        <v>-34.28685542230778</v>
       </c>
       <c r="W11">
-        <v>-56.57371845000125</v>
+        <v>-56.57371840865562</v>
       </c>
       <c r="X11">
-        <v>-82.86058111000057</v>
+        <v>-82.86058106886958</v>
       </c>
       <c r="Y11">
-        <v>-134.8605506699987</v>
+        <v>-134.8605506008171</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1497,19 +1497,19 @@
         <v>17</v>
       </c>
       <c r="AD11">
-        <v>-3.599997324000014</v>
+        <v>-3.599997326271932</v>
       </c>
       <c r="AE11">
-        <v>-11.99999349000154</v>
+        <v>-11.99999349140126</v>
       </c>
       <c r="AF11">
-        <v>-20.28686526000092</v>
+        <v>-20.2868652474981</v>
       </c>
       <c r="AG11">
-        <v>-30.28685814999881</v>
+        <v>-30.28685814762503</v>
       </c>
       <c r="AH11">
-        <v>-51.57372272000066</v>
+        <v>-51.57372273241526</v>
       </c>
       <c r="AK11">
         <v>6</v>
@@ -1562,19 +1562,19 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>10.80002607000188</v>
+        <v>10.80002609510029</v>
       </c>
       <c r="D12">
-        <v>35.00037275999875</v>
+        <v>35.00037284764585</v>
       </c>
       <c r="E12">
-        <v>55.00056439000309</v>
+        <v>55.00056452350418</v>
       </c>
       <c r="F12">
-        <v>78.00101261000054</v>
+        <v>78.00101280292984</v>
       </c>
       <c r="G12">
-        <v>125.00138797</v>
+        <v>125.001388294917</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -1583,19 +1583,19 @@
         <v>15</v>
       </c>
       <c r="L12">
-        <v>3.600061343997368</v>
+        <v>3.600061337852821</v>
       </c>
       <c r="M12">
-        <v>25.99969059000432</v>
+        <v>25.99969060102012</v>
       </c>
       <c r="N12">
-        <v>47.99978901999202</v>
+        <v>47.99978906347678</v>
       </c>
       <c r="O12">
-        <v>72.99984089999998</v>
+        <v>72.99984098487403</v>
       </c>
       <c r="P12">
-        <v>138.9998196699999</v>
+        <v>138.9998199096335</v>
       </c>
       <c r="S12">
         <v>4</v>
@@ -1604,19 +1604,19 @@
         <v>16</v>
       </c>
       <c r="U12">
-        <v>-13.20008563800184</v>
+        <v>-13.20008564769705</v>
       </c>
       <c r="V12">
-        <v>-48.00031909000245</v>
+        <v>-48.00031917250999</v>
       </c>
       <c r="W12">
-        <v>-85.0002543000046</v>
+        <v>-85.00025445558458</v>
       </c>
       <c r="X12">
-        <v>-123.0006803200013</v>
+        <v>-123.000680566216</v>
       </c>
       <c r="Y12">
-        <v>-206.0010441199993</v>
+        <v>-206.0010445900461</v>
       </c>
       <c r="AB12">
         <v>4</v>
@@ -1625,19 +1625,19 @@
         <v>17</v>
       </c>
       <c r="AD12">
-        <v>-4.799955420000515</v>
+        <v>-4.799955436669279</v>
       </c>
       <c r="AE12">
-        <v>-14.99991890999991</v>
+        <v>-14.99991894992809</v>
       </c>
       <c r="AF12">
-        <v>-21.00027775000126</v>
+        <v>-21.0002777804898</v>
       </c>
       <c r="AG12">
-        <v>-32.00024271999973</v>
+        <v>-32.00024275065061</v>
       </c>
       <c r="AH12">
-        <v>-55.00026702999958</v>
+        <v>-55.00026710731436</v>
       </c>
       <c r="AK12">
         <v>4</v>
@@ -1667,7 +1667,7 @@
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AW12">
         <v>0</v>
@@ -1690,19 +1690,19 @@
         <v>14</v>
       </c>
       <c r="C13">
-        <v>1.179638339999997</v>
+        <v>1.179638330373564</v>
       </c>
       <c r="D13">
-        <v>0.001358759999789</v>
+        <v>0.0013587568375896</v>
       </c>
       <c r="E13">
-        <v>1.967431979999901</v>
+        <v>1.967431970821622</v>
       </c>
       <c r="F13">
-        <v>1.96836524999992</v>
+        <v>1.968365240005141</v>
       </c>
       <c r="G13">
-        <v>6.901234479999971</v>
+        <v>6.901234426738142</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1711,19 +1711,19 @@
         <v>15</v>
       </c>
       <c r="L13">
-        <v>1.779265128000134</v>
+        <v>1.779265107571518</v>
       </c>
       <c r="M13">
-        <v>6.931924420000541</v>
+        <v>6.9319243501036</v>
       </c>
       <c r="N13">
-        <v>9.898405219999404</v>
+        <v>9.89840512301862</v>
       </c>
       <c r="O13">
-        <v>16.83032850999916</v>
+        <v>16.83032834539245</v>
       </c>
       <c r="P13">
-        <v>25.72936160999916</v>
+        <v>25.72936137297074</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -1732,19 +1732,19 @@
         <v>16</v>
       </c>
       <c r="U13">
-        <v>-1.779891648000103</v>
+        <v>-1.779891633249918</v>
       </c>
       <c r="V13">
-        <v>-5.932857569999669</v>
+        <v>-5.932857510476879</v>
       </c>
       <c r="W13">
-        <v>-9.899346449999484</v>
+        <v>-9.899346351353415</v>
       </c>
       <c r="X13">
-        <v>-14.86687469000071</v>
+        <v>-14.86687455248739</v>
       </c>
       <c r="Y13">
-        <v>-22.76611373000151</v>
+        <v>-22.76611352323516</v>
       </c>
       <c r="AB13">
         <v>1</v>
@@ -1753,19 +1753,19 @@
         <v>17</v>
       </c>
       <c r="AD13">
-        <v>-0.5792680500001097</v>
+        <v>-0.579268046449215</v>
       </c>
       <c r="AE13">
-        <v>-2.000732050000124</v>
+        <v>-2.000732032065116</v>
       </c>
       <c r="AF13">
-        <v>-3.966485920000196</v>
+        <v>-3.966485872643716</v>
       </c>
       <c r="AG13">
-        <v>-5.932546960000309</v>
+        <v>-5.932546901271735</v>
       </c>
       <c r="AH13">
-        <v>-8.899343579999822</v>
+        <v>-8.899343498050939</v>
       </c>
       <c r="AK13">
         <v>1</v>
@@ -1795,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>-1.818989403545856E-12</v>
       </c>
       <c r="AW13">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="AZ13">
-        <v>-1.818989403545856E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:52">
@@ -1818,19 +1818,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>18.60000012000092</v>
+        <v>18.60000000358559</v>
       </c>
       <c r="D14">
-        <v>62.00000041000567</v>
+        <v>62.00000001244371</v>
       </c>
       <c r="E14">
-        <v>96.00000062001163</v>
+        <v>96.00000001958324</v>
       </c>
       <c r="F14">
-        <v>135.0000009000032</v>
+        <v>135.000000029193</v>
       </c>
       <c r="G14">
-        <v>203.0000014099878</v>
+        <v>203.0000000495893</v>
       </c>
       <c r="J14">
         <v>17</v>
@@ -1839,19 +1839,19 @@
         <v>15</v>
       </c>
       <c r="L14">
-        <v>5.999999999978172</v>
+        <v>5.999999998257408</v>
       </c>
       <c r="M14">
-        <v>35.00000011999145</v>
+        <v>34.99999999652937</v>
       </c>
       <c r="N14">
-        <v>64.00000023003304</v>
+        <v>63.99999999772626</v>
       </c>
       <c r="O14">
-        <v>101.000000369997</v>
+        <v>100.9999999967476</v>
       </c>
       <c r="P14">
-        <v>189.0000007699928</v>
+        <v>188.9999999996362</v>
       </c>
       <c r="S14">
         <v>17</v>
@@ -1860,19 +1860,19 @@
         <v>16</v>
       </c>
       <c r="U14">
-        <v>-20.40000010799849</v>
+        <v>-20.40000000174769</v>
       </c>
       <c r="V14">
-        <v>-73.00000040999294</v>
+        <v>-73.00000001023545</v>
       </c>
       <c r="W14">
-        <v>-122.0000006699956</v>
+        <v>-122.00000001646</v>
       </c>
       <c r="X14">
-        <v>-174.000001010003</v>
+        <v>-174.00000002243</v>
       </c>
       <c r="Y14">
-        <v>-288.000001689994</v>
+        <v>-288.0000000416803</v>
       </c>
       <c r="AB14">
         <v>17</v>
@@ -1881,19 +1881,19 @@
         <v>17</v>
       </c>
       <c r="AD14">
-        <v>-9.000000035999619</v>
+        <v>-9.000000000980435</v>
       </c>
       <c r="AE14">
-        <v>-22.00000010000531</v>
+        <v>-22.00000000077761</v>
       </c>
       <c r="AF14">
-        <v>-42.00000021000142</v>
+        <v>-42.00000000300315</v>
       </c>
       <c r="AG14">
-        <v>-66.00000031999662</v>
+        <v>-66.00000000564523</v>
       </c>
       <c r="AH14">
-        <v>-105.0000005100028</v>
+        <v>-105.0000000060945</v>
       </c>
       <c r="AK14">
         <v>17</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -1946,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>9.21398929800216</v>
+        <v>9.213989289310121</v>
       </c>
       <c r="D15">
-        <v>31.35665218999929</v>
+        <v>31.3566521741559</v>
       </c>
       <c r="E15">
-        <v>51.71330156000022</v>
+        <v>51.71330152913561</v>
       </c>
       <c r="F15">
-        <v>76.71330567000041</v>
+        <v>76.71330563065749</v>
       </c>
       <c r="G15">
-        <v>117.4266093299975</v>
+        <v>117.4266092430989</v>
       </c>
       <c r="J15">
         <v>15</v>
@@ -1967,19 +1967,19 @@
         <v>15</v>
       </c>
       <c r="L15">
-        <v>5.013986573998409</v>
+        <v>5.013986578771437</v>
       </c>
       <c r="M15">
-        <v>25.71328962000189</v>
+        <v>25.71328964066925</v>
       </c>
       <c r="N15">
-        <v>46.42658048000158</v>
+        <v>46.42658051265971</v>
       </c>
       <c r="O15">
-        <v>65.7832243399971</v>
+        <v>65.78322438042596</v>
       </c>
       <c r="P15">
-        <v>122.2098054599992</v>
+        <v>122.2098055422575</v>
       </c>
       <c r="S15">
         <v>15</v>
@@ -1988,19 +1988,19 @@
         <v>16</v>
       </c>
       <c r="U15">
-        <v>-9.813988554000389</v>
+        <v>-9.81398855452062</v>
       </c>
       <c r="V15">
-        <v>-41.71329345999948</v>
+        <v>-41.71329345996674</v>
       </c>
       <c r="W15">
-        <v>-69.42658957000276</v>
+        <v>-69.42658956460764</v>
       </c>
       <c r="X15">
-        <v>-105.7832356399995</v>
+        <v>-105.7832356400468</v>
       </c>
       <c r="Y15">
-        <v>-179.2098266899993</v>
+        <v>-179.2098266920402</v>
       </c>
       <c r="AB15">
         <v>15</v>
@@ -2009,19 +2009,19 @@
         <v>17</v>
       </c>
       <c r="AD15">
-        <v>-2.99999908800055</v>
+        <v>-2.999999093798124</v>
       </c>
       <c r="AE15">
-        <v>-12.35664619999898</v>
+        <v>-12.35664620319494</v>
       </c>
       <c r="AF15">
-        <v>-25.71329298000001</v>
+        <v>-25.71329298445199</v>
       </c>
       <c r="AG15">
-        <v>-36.71329267000056</v>
+        <v>-36.71329267377587</v>
       </c>
       <c r="AH15">
-        <v>-59.4265861899994</v>
+        <v>-59.42658619457598</v>
       </c>
       <c r="AK15">
         <v>15</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>-7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AT15">
         <v>15</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="AW15">
-        <v>-7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AX15">
         <v>0</v>
@@ -2074,19 +2074,19 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>7.075708008001129</v>
+        <v>7.075707983584834</v>
       </c>
       <c r="D16">
-        <v>28.58569138999973</v>
+        <v>28.58569126288603</v>
       </c>
       <c r="E16">
-        <v>46.37853964999977</v>
+        <v>46.37853946318046</v>
       </c>
       <c r="F16">
-        <v>65.17138711999996</v>
+        <v>65.17138684362635</v>
       </c>
       <c r="G16">
-        <v>102.7570809999988</v>
+        <v>102.757080558692</v>
       </c>
       <c r="J16">
         <v>16</v>
@@ -2095,19 +2095,19 @@
         <v>15</v>
       </c>
       <c r="L16">
-        <v>5.400002616002894</v>
+        <v>5.400002602033055</v>
       </c>
       <c r="M16">
-        <v>25.37853958000414</v>
+        <v>25.37853952825026</v>
       </c>
       <c r="N16">
-        <v>47.17139038999812</v>
+        <v>47.17139027917437</v>
       </c>
       <c r="O16">
-        <v>65.75708518000101</v>
+        <v>65.75708501580084</v>
       </c>
       <c r="P16">
-        <v>114.9284759399998</v>
+        <v>114.928475654473</v>
       </c>
       <c r="S16">
         <v>16</v>
@@ -2116,19 +2116,19 @@
         <v>16</v>
       </c>
       <c r="U16">
-        <v>-11.151414750002</v>
+        <v>-11.1514147063881</v>
       </c>
       <c r="V16">
-        <v>-40.37854218000211</v>
+        <v>-40.3785420411059</v>
       </c>
       <c r="W16">
-        <v>-68.96423670999866</v>
+        <v>-68.96423647592019</v>
       </c>
       <c r="X16">
-        <v>-98.54993452999952</v>
+        <v>-98.54993417555488</v>
       </c>
       <c r="Y16">
-        <v>-163.5141681599962</v>
+        <v>-163.5141675638461</v>
       </c>
       <c r="AB16">
         <v>16</v>
@@ -2137,19 +2137,19 @@
         <v>17</v>
       </c>
       <c r="AD16">
-        <v>-4.07570682000005</v>
+        <v>-4.075706794371399</v>
       </c>
       <c r="AE16">
-        <v>-15.79284645999996</v>
+        <v>-15.79284642238235</v>
       </c>
       <c r="AF16">
-        <v>-22.58569168999838</v>
+        <v>-22.58569163875927</v>
       </c>
       <c r="AG16">
-        <v>-34.17138255000009</v>
+        <v>-34.17138246258764</v>
       </c>
       <c r="AH16">
-        <v>-55.96423112000048</v>
+        <v>-55.96423096856233</v>
       </c>
       <c r="AK16">
         <v>16</v>
@@ -2158,7 +2158,7 @@
         <v>11</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AN16">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>12</v>
       </c>
       <c r="AV16">
-        <v>7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AW16">
         <v>0</v>
@@ -2202,19 +2202,19 @@
         <v>14</v>
       </c>
       <c r="C17">
-        <v>0.6000001200002316</v>
+        <v>0.6000001264928869</v>
       </c>
       <c r="D17">
-        <v>4.999998949999963</v>
+        <v>4.999998969865146</v>
       </c>
       <c r="E17">
-        <v>7.999998350000169</v>
+        <v>7.999998370306002</v>
       </c>
       <c r="F17">
-        <v>12.99999691000016</v>
+        <v>12.99999693362133</v>
       </c>
       <c r="G17">
-        <v>19.99999617999969</v>
+        <v>19.9999962325121</v>
       </c>
       <c r="J17">
         <v>11</v>
@@ -2223,19 +2223,19 @@
         <v>15</v>
       </c>
       <c r="L17">
-        <v>2.999999159999788</v>
+        <v>2.999999153799763</v>
       </c>
       <c r="M17">
-        <v>9.805228660000466</v>
+        <v>9.805228655977771</v>
       </c>
       <c r="N17">
-        <v>17.20784241000001</v>
+        <v>17.2078424019719</v>
       </c>
       <c r="O17">
-        <v>23.61045688999912</v>
+        <v>23.61045688708873</v>
       </c>
       <c r="P17">
-        <v>38.41568508999899</v>
+        <v>38.41568508879755</v>
       </c>
       <c r="S17">
         <v>11</v>
@@ -2244,19 +2244,19 @@
         <v>16</v>
       </c>
       <c r="U17">
-        <v>-3.841568375999486</v>
+        <v>-3.841568381152683</v>
       </c>
       <c r="V17">
-        <v>-10.80522861999907</v>
+        <v>-10.80522863242641</v>
       </c>
       <c r="W17">
-        <v>-17.80522801999996</v>
+        <v>-17.80522804468637</v>
       </c>
       <c r="X17">
-        <v>-26.80522624999958</v>
+        <v>-26.80522627481787</v>
       </c>
       <c r="Y17">
-        <v>-42.61045388000093</v>
+        <v>-42.61045393225959</v>
       </c>
       <c r="AB17">
         <v>11</v>
@@ -2265,19 +2265,19 @@
         <v>17</v>
       </c>
       <c r="AD17">
-        <v>-1.19999992800058</v>
+        <v>-1.199999928916441</v>
       </c>
       <c r="AE17">
-        <v>-2.999999529999968</v>
+        <v>-2.999999525536623</v>
       </c>
       <c r="AF17">
-        <v>-6.402614079999694</v>
+        <v>-6.402614079478553</v>
       </c>
       <c r="AG17">
-        <v>-9.402613900000231</v>
+        <v>-9.402613903946984</v>
       </c>
       <c r="AH17">
-        <v>-14.80522839000014</v>
+        <v>-14.80522839045079</v>
       </c>
       <c r="AK17">
         <v>11</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AP17">
         <v>0</v>
@@ -2307,10 +2307,10 @@
         <v>12</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>-1.818989403545856E-12</v>
       </c>
       <c r="AW17">
-        <v>1.818989403545856E-12</v>
+        <v>0</v>
       </c>
       <c r="AX17">
         <v>0</v>
@@ -2330,19 +2330,19 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <v>4.680000529333483E-07</v>
+        <v>4.642975000024309E-07</v>
       </c>
       <c r="D18">
-        <v>0.999999669999852</v>
+        <v>0.9999996716620672</v>
       </c>
       <c r="E18">
-        <v>2.000000330000034</v>
+        <v>2.000000331040496</v>
       </c>
       <c r="F18">
-        <v>3.798881639999991</v>
+        <v>3.798881634242776</v>
       </c>
       <c r="G18">
-        <v>4.000001229999953</v>
+        <v>4.000001212472284</v>
       </c>
       <c r="J18">
         <v>14</v>
@@ -2351,19 +2351,19 @@
         <v>15</v>
       </c>
       <c r="L18">
-        <v>1.200000162000379</v>
+        <v>1.200000161885782</v>
       </c>
       <c r="M18">
-        <v>3.798884429999816</v>
+        <v>3.798884414763052</v>
       </c>
       <c r="N18">
-        <v>6.396649630000411</v>
+        <v>6.39664962692359</v>
       </c>
       <c r="O18">
-        <v>9.195533280000291</v>
+        <v>9.195533263554807</v>
       </c>
       <c r="P18">
-        <v>14.99441773999979</v>
+        <v>14.99441771895545</v>
       </c>
       <c r="S18">
         <v>14</v>
@@ -2372,19 +2372,19 @@
         <v>16</v>
       </c>
       <c r="U18">
-        <v>-1.079329722000239</v>
+        <v>-1.079329721406793</v>
       </c>
       <c r="V18">
-        <v>-3.798883630000091</v>
+        <v>-3.798883619807839</v>
       </c>
       <c r="W18">
-        <v>-6.597766530000172</v>
+        <v>-6.597766518495973</v>
       </c>
       <c r="X18">
-        <v>-8.597767580000436</v>
+        <v>-8.597767569507596</v>
       </c>
       <c r="Y18">
-        <v>-13.19553441000016</v>
+        <v>-13.19553438352432</v>
       </c>
       <c r="AB18">
         <v>14</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="AD18">
-        <v>-5.459999101731228E-07</v>
+        <v>-5.432589205156546E-07</v>
       </c>
       <c r="AE18">
-        <v>-1.798881920000213</v>
+        <v>-1.798881918984534</v>
       </c>
       <c r="AF18">
-        <v>-2.7988826899998</v>
+        <v>-2.798882685874105</v>
       </c>
       <c r="AG18">
-        <v>-3.798883049999858</v>
+        <v>-3.798883054850421</v>
       </c>
       <c r="AH18">
-        <v>-6.597766079999928</v>
+        <v>-6.597766080826204</v>
       </c>
       <c r="AK18">
         <v>14</v>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>-1.818989403545856E-12</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
         <v>0</v>
@@ -2435,16 +2435,16 @@
         <v>12</v>
       </c>
       <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
         <v>9.094947017729282E-13</v>
       </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
       <c r="AX18">
         <v>0</v>
       </c>
       <c r="AY18">
-        <v>9.094947017729282E-13</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -2458,19 +2458,19 @@
         <v>14</v>
       </c>
       <c r="C19">
-        <v>0.8621510700000954</v>
+        <v>0.8621510648970343</v>
       </c>
       <c r="D19">
-        <v>0.4369260400002304</v>
+        <v>0.4369260300389896</v>
       </c>
       <c r="E19">
-        <v>1.873844510000481</v>
+        <v>1.873844485562245</v>
       </c>
       <c r="F19">
-        <v>2.863099769999849</v>
+        <v>2.863099763517084</v>
       </c>
       <c r="G19">
-        <v>3.361961969999925</v>
+        <v>3.361961916344399</v>
       </c>
       <c r="J19">
         <v>13</v>
@@ -2479,19 +2479,19 @@
         <v>15</v>
       </c>
       <c r="L19">
-        <v>2.092864019999524</v>
+        <v>2.092864031181307</v>
       </c>
       <c r="M19">
-        <v>9.183248329999969</v>
+        <v>9.183248392419046</v>
       </c>
       <c r="N19">
-        <v>13.72254362000149</v>
+        <v>13.72254369796883</v>
       </c>
       <c r="O19">
-        <v>20.68800765000015</v>
+        <v>20.68800776918397</v>
       </c>
       <c r="P19">
-        <v>36.84746768999958</v>
+        <v>36.84746787416043</v>
       </c>
       <c r="S19">
         <v>13</v>
@@ -2500,19 +2500,19 @@
         <v>16</v>
       </c>
       <c r="U19">
-        <v>-2.092864350001037</v>
+        <v>-2.092864351840035</v>
       </c>
       <c r="V19">
-        <v>-7.579732710000826</v>
+        <v>-7.579732743161003</v>
       </c>
       <c r="W19">
-        <v>-11.67136005999964</v>
+        <v>-11.67136011822367</v>
       </c>
       <c r="X19">
-        <v>-16.64758108000115</v>
+        <v>-16.6475811535729</v>
       </c>
       <c r="Y19">
-        <v>-27.52733087000161</v>
+        <v>-27.52733097239525</v>
       </c>
       <c r="AB19">
         <v>13</v>
@@ -2521,19 +2521,19 @@
         <v>17</v>
       </c>
       <c r="AD19">
-        <v>-0.8621505900000557</v>
+        <v>-0.8621505970777434</v>
       </c>
       <c r="AE19">
-        <v>-3.603515450000032</v>
+        <v>-3.603515447146947</v>
       </c>
       <c r="AF19">
-        <v>-5.091625159999694</v>
+        <v>-5.091625182193184</v>
       </c>
       <c r="AG19">
-        <v>-7.695139670000572</v>
+        <v>-7.695139693467354</v>
       </c>
       <c r="AH19">
-        <v>-12.62016428000015</v>
+        <v>-12.6201643170748</v>
       </c>
       <c r="AK19">
         <v>13</v>
@@ -2563,7 +2563,7 @@
         <v>12</v>
       </c>
       <c r="AV19">
-        <v>1.818989403545856E-12</v>
+        <v>-1.818989403545856E-12</v>
       </c>
       <c r="AW19">
         <v>0</v>
@@ -2586,19 +2586,19 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>4.200002021999353</v>
+        <v>4.20000201244784</v>
       </c>
       <c r="D20">
-        <v>16.0000059799986</v>
+        <v>16.0000059416534</v>
       </c>
       <c r="E20">
-        <v>23.00001156999951</v>
+        <v>23.00001151821744</v>
       </c>
       <c r="F20">
-        <v>33.00001592999979</v>
+        <v>33.00001584942038</v>
       </c>
       <c r="G20">
-        <v>50.00002296000093</v>
+        <v>50.00002284315997</v>
       </c>
       <c r="J20">
         <v>12</v>
@@ -2607,19 +2607,19 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>6.427877946000081</v>
+        <v>6.427877927470036</v>
       </c>
       <c r="M20">
-        <v>22.42626407999705</v>
+        <v>22.42626401052439</v>
       </c>
       <c r="N20">
-        <v>37.42627179999909</v>
+        <v>37.42627168889703</v>
       </c>
       <c r="O20">
-        <v>55.85253435999948</v>
+        <v>55.85253419381479</v>
       </c>
       <c r="P20">
-        <v>88.85255995999978</v>
+        <v>88.85255969403443</v>
       </c>
       <c r="S20">
         <v>12</v>
@@ -2628,19 +2628,19 @@
         <v>16</v>
       </c>
       <c r="U20">
-        <v>-7.627879109995774</v>
+        <v>-7.627879081584979</v>
       </c>
       <c r="V20">
-        <v>-26.71314103000077</v>
+        <v>-26.71314094517038</v>
       </c>
       <c r="W20">
-        <v>-43.42627508999794</v>
+        <v>-43.42627498051115</v>
       </c>
       <c r="X20">
-        <v>-61.13941117000104</v>
+        <v>-61.13941100014199</v>
       </c>
       <c r="Y20">
-        <v>-96.13943631000076</v>
+        <v>-96.13943604816632</v>
       </c>
       <c r="AB20">
         <v>12</v>
@@ -2649,19 +2649,19 @@
         <v>17</v>
       </c>
       <c r="AD20">
-        <v>-3.600001644001168</v>
+        <v>-3.600001639232687</v>
       </c>
       <c r="AE20">
-        <v>-11.00000558000011</v>
+        <v>-11.00000555021324</v>
       </c>
       <c r="AF20">
-        <v>-16.71313320000172</v>
+        <v>-16.71313317063414</v>
       </c>
       <c r="AG20">
-        <v>-25.71313806999843</v>
+        <v>-25.71313799740892</v>
       </c>
       <c r="AH20">
-        <v>-42.42627145000006</v>
+        <v>-42.42627133926089</v>
       </c>
       <c r="AK20">
         <v>12</v>
@@ -2670,7 +2670,7 @@
         <v>11</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>7.275957614183426E-12</v>
       </c>
       <c r="AN20">
         <v>0</v>
@@ -2694,13 +2694,13 @@
         <v>0</v>
       </c>
       <c r="AW20">
-        <v>-3.637978807091713E-12</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AY20">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -2714,19 +2714,19 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>14.99998574399979</v>
+        <v>14.99998573852099</v>
       </c>
       <c r="D21">
-        <v>46.99996114999885</v>
+        <v>46.99996113438465</v>
       </c>
       <c r="E21">
-        <v>79.99993252000058</v>
+        <v>79.99993249886938</v>
       </c>
       <c r="F21">
-        <v>115.9998992399996</v>
+        <v>115.999899212009</v>
       </c>
       <c r="G21">
-        <v>182.9998483</v>
+        <v>182.9998482486389</v>
       </c>
       <c r="J21">
         <v>28</v>
@@ -2735,19 +2735,19 @@
         <v>15</v>
       </c>
       <c r="L21">
-        <v>6.599992518000363</v>
+        <v>6.599992520674277</v>
       </c>
       <c r="M21">
-        <v>23.99997513999915</v>
+        <v>23.99997513739436</v>
       </c>
       <c r="N21">
-        <v>41.99995647000105</v>
+        <v>41.99995646569369</v>
       </c>
       <c r="O21">
-        <v>62.99993525999889</v>
+        <v>62.99993525247555</v>
       </c>
       <c r="P21">
-        <v>125.9998686899999</v>
+        <v>125.9998686760409</v>
       </c>
       <c r="S21">
         <v>28</v>
@@ -2756,19 +2756,19 @@
         <v>16</v>
       </c>
       <c r="U21">
-        <v>-14.99998735800364</v>
+        <v>-14.99998735492227</v>
       </c>
       <c r="V21">
-        <v>-55.99994907999826</v>
+        <v>-55.99994907019209</v>
       </c>
       <c r="W21">
-        <v>-96.99991486999896</v>
+        <v>-96.99991485308055</v>
       </c>
       <c r="X21">
-        <v>-141.9998730799998</v>
+        <v>-141.999873050001</v>
       </c>
       <c r="Y21">
-        <v>-242.999782789997</v>
+        <v>-242.999782737741</v>
       </c>
       <c r="AB21">
         <v>28</v>
@@ -2777,19 +2777,19 @@
         <v>17</v>
       </c>
       <c r="AD21">
-        <v>-2.999999315999958</v>
+        <v>-2.999999312414729</v>
       </c>
       <c r="AE21">
-        <v>-14.99998536999965</v>
+        <v>-14.99998536548492</v>
       </c>
       <c r="AF21">
-        <v>-27.99997337999957</v>
+        <v>-27.99997337686455</v>
       </c>
       <c r="AG21">
-        <v>-36.99996707999981</v>
+        <v>-36.9999670733514</v>
       </c>
       <c r="AH21">
-        <v>-62.9999421399998</v>
+        <v>-62.99994212513048</v>
       </c>
       <c r="AK21">
         <v>28</v>
@@ -2807,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AT21">
         <v>28</v>
@@ -2819,7 +2819,7 @@
         <v>12</v>
       </c>
       <c r="AV21">
-        <v>7.275957614183426E-12</v>
+        <v>0</v>
       </c>
       <c r="AW21">
         <v>0</v>
@@ -2842,19 +2842,19 @@
         <v>14</v>
       </c>
       <c r="C22">
-        <v>8.786008955999932</v>
+        <v>8.786008962588312</v>
       </c>
       <c r="D22">
-        <v>27.64334881000013</v>
+        <v>27.64334882755339</v>
       </c>
       <c r="E22">
-        <v>42.28669640000044</v>
+        <v>42.28669642978821</v>
       </c>
       <c r="F22">
-        <v>61.28669648999858</v>
+        <v>61.28669653093129</v>
       </c>
       <c r="G22">
-        <v>98.57338957999946</v>
+        <v>98.57338965842156</v>
       </c>
       <c r="J22">
         <v>18</v>
@@ -2863,19 +2863,19 @@
         <v>15</v>
       </c>
       <c r="L22">
-        <v>2.186014086000796</v>
+        <v>2.186014072813123</v>
       </c>
       <c r="M22">
-        <v>19.28670561999934</v>
+        <v>19.28670561085709</v>
       </c>
       <c r="N22">
-        <v>36.57341228000223</v>
+        <v>36.57341225674099</v>
       </c>
       <c r="O22">
-        <v>53.21676387999833</v>
+        <v>53.21676384071907</v>
       </c>
       <c r="P22">
-        <v>102.7901740999987</v>
+        <v>102.7901740349334</v>
       </c>
       <c r="S22">
         <v>18</v>
@@ -2884,19 +2884,19 @@
         <v>16</v>
       </c>
       <c r="U22">
-        <v>-9.986011356000745</v>
+        <v>-9.986011356397285</v>
       </c>
       <c r="V22">
-        <v>-35.28670392000095</v>
+        <v>-35.28670391237756</v>
       </c>
       <c r="W22">
-        <v>-62.57340471000134</v>
+        <v>-62.57340471484349</v>
       </c>
       <c r="X22">
-        <v>-90.21675157000028</v>
+        <v>-90.21675157178106</v>
       </c>
       <c r="Y22">
-        <v>-152.79016056</v>
+        <v>-152.790160569004</v>
       </c>
       <c r="AB22">
         <v>18</v>
@@ -2905,19 +2905,19 @@
         <v>17</v>
       </c>
       <c r="AD22">
-        <v>-2.999999652000497</v>
+        <v>-2.9999996536867</v>
       </c>
       <c r="AE22">
-        <v>-9.643350610000198</v>
+        <v>-9.643350607288085</v>
       </c>
       <c r="AF22">
-        <v>-15.2867056999994</v>
+        <v>-15.28670569729456</v>
       </c>
       <c r="AG22">
-        <v>-26.2867038899999</v>
+        <v>-26.28670388704268</v>
       </c>
       <c r="AH22">
-        <v>-47.57340448000014</v>
+        <v>-47.57340447404022</v>
       </c>
       <c r="AK22">
         <v>18</v>
@@ -2926,16 +2926,16 @@
         <v>11</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>-3.637978807091713E-12</v>
       </c>
       <c r="AN22">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -2947,10 +2947,10 @@
         <v>12</v>
       </c>
       <c r="AV22">
-        <v>3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AW22">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AX22">
         <v>0</v>
@@ -2970,19 +2970,19 @@
         <v>14</v>
       </c>
       <c r="C23">
-        <v>0.724294566000026</v>
+        <v>0.7242945675205874</v>
       </c>
       <c r="D23">
-        <v>1.414316099999951</v>
+        <v>1.414316103221267</v>
       </c>
       <c r="E23">
-        <v>2.621475059999966</v>
+        <v>2.621475062818945</v>
       </c>
       <c r="F23">
-        <v>2.828632399999833</v>
+        <v>2.828632400119432</v>
       </c>
       <c r="G23">
-        <v>4.242952739999964</v>
+        <v>4.242952750928907</v>
       </c>
       <c r="J23">
         <v>19</v>
@@ -2991,19 +2991,19 @@
         <v>15</v>
       </c>
       <c r="L23">
-        <v>1.200000792000083</v>
+        <v>1.200000793099207</v>
       </c>
       <c r="M23">
-        <v>6.62147251999977</v>
+        <v>6.621472525700938</v>
       </c>
       <c r="N23">
-        <v>10.82862951000061</v>
+        <v>10.82862950633716</v>
       </c>
       <c r="O23">
-        <v>13.24294840999937</v>
+        <v>13.2429484080817</v>
       </c>
       <c r="P23">
-        <v>21.0715823000005</v>
+        <v>21.07158230108553</v>
       </c>
       <c r="S23">
         <v>19</v>
@@ -3012,19 +3012,19 @@
         <v>16</v>
       </c>
       <c r="U23">
-        <v>-1.448589882000306</v>
+        <v>-1.448589882718807</v>
       </c>
       <c r="V23">
-        <v>-4.621475929999178</v>
+        <v>-4.621475925547202</v>
       </c>
       <c r="W23">
-        <v>-9.035791269999663</v>
+        <v>-9.035791276551208</v>
       </c>
       <c r="X23">
-        <v>-10.45010919999822</v>
+        <v>-10.45010919527658</v>
       </c>
       <c r="Y23">
-        <v>-16.48590160999993</v>
+        <v>-16.48590161425545</v>
       </c>
       <c r="AB23">
         <v>19</v>
@@ -3033,19 +3033,19 @@
         <v>17</v>
       </c>
       <c r="AD23">
-        <v>-0.1242948720002914</v>
+        <v>-0.1242948693889047</v>
       </c>
       <c r="AE23">
-        <v>-3.207156800000575</v>
+        <v>-3.207156804583974</v>
       </c>
       <c r="AF23">
-        <v>-4.414313680000305</v>
+        <v>-4.414313684395438</v>
       </c>
       <c r="AG23">
-        <v>-6.828630010000779</v>
+        <v>-6.828630019861521</v>
       </c>
       <c r="AH23">
-        <v>-9.035788999999568</v>
+        <v>-9.03578901299943</v>
       </c>
       <c r="AK23">
         <v>19</v>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1.818989403545856E-12</v>
       </c>
       <c r="AP23">
         <v>1.818989403545856E-12</v>
       </c>
       <c r="AQ23">
-        <v>1.818989403545856E-12</v>
+        <v>0</v>
       </c>
       <c r="AT23">
         <v>19</v>
@@ -3081,13 +3081,13 @@
         <v>0</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>-1.818989403545856E-12</v>
       </c>
       <c r="AY23">
         <v>0</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.818989403545856E-12</v>
       </c>
     </row>
     <row r="24" spans="1:52">
@@ -3098,19 +3098,19 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>2.400000294000165</v>
+        <v>2.400000293921494</v>
       </c>
       <c r="D24">
-        <v>9.999999560000106</v>
+        <v>9.999999569986358</v>
       </c>
       <c r="E24">
-        <v>14.00000231000013</v>
+        <v>14.00000232248112</v>
       </c>
       <c r="F24">
-        <v>23.00004007000007</v>
+        <v>23.00004009925988</v>
       </c>
       <c r="G24">
-        <v>37.00000188000013</v>
+        <v>37.00000190118499</v>
       </c>
       <c r="J24">
         <v>20</v>
@@ -3119,19 +3119,19 @@
         <v>15</v>
       </c>
       <c r="L24">
-        <v>5.400024227999893</v>
+        <v>5.400024233982549</v>
       </c>
       <c r="M24">
-        <v>22.19480651000049</v>
+        <v>22.19480651140657</v>
       </c>
       <c r="N24">
-        <v>35.79227057000026</v>
+        <v>35.79227059028199</v>
       </c>
       <c r="O24">
-        <v>57.38969382999858</v>
+        <v>57.38969384473967</v>
       </c>
       <c r="P24">
-        <v>91.58454188000178</v>
+        <v>91.5845419070356</v>
       </c>
       <c r="S24">
         <v>20</v>
@@ -3140,19 +3140,19 @@
         <v>16</v>
       </c>
       <c r="U24">
-        <v>-7.558429415999853</v>
+        <v>-7.558429414995771</v>
       </c>
       <c r="V24">
-        <v>-23.19480971999837</v>
+        <v>-23.19480973053942</v>
       </c>
       <c r="W24">
-        <v>-40.19484912000007</v>
+        <v>-40.1948491396779</v>
       </c>
       <c r="X24">
-        <v>-57.19488694999745</v>
+        <v>-57.19488698576242</v>
       </c>
       <c r="Y24">
-        <v>-94.3896963799998</v>
+        <v>-94.38969642186019</v>
       </c>
       <c r="AB24">
         <v>20</v>
@@ -3161,19 +3161,19 @@
         <v>17</v>
       </c>
       <c r="AD24">
-        <v>-2.40000021600008</v>
+        <v>-2.400000220361107</v>
       </c>
       <c r="AE24">
-        <v>-10.00003771000047</v>
+        <v>-10.00003770992316</v>
       </c>
       <c r="AF24">
-        <v>-13.59746343999996</v>
+        <v>-13.59746345956773</v>
       </c>
       <c r="AG24">
-        <v>-22.59746297999936</v>
+        <v>-22.59746300226197</v>
       </c>
       <c r="AH24">
-        <v>-38.19484534000003</v>
+        <v>-38.19484535594529</v>
       </c>
       <c r="AK24">
         <v>20</v>
@@ -3226,19 +3226,19 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>11.99999962199763</v>
+        <v>11.99999963239134</v>
       </c>
       <c r="D25">
-        <v>46.00000042000102</v>
+        <v>46.00000049617665</v>
       </c>
       <c r="E25">
-        <v>69.99999578999814</v>
+        <v>69.99999585342448</v>
       </c>
       <c r="F25">
-        <v>100.0000000599994</v>
+        <v>100.0000001736462</v>
       </c>
       <c r="G25">
-        <v>162.0000033200013</v>
+        <v>162.0000035157445</v>
       </c>
       <c r="J25">
         <v>27</v>
@@ -3247,19 +3247,19 @@
         <v>15</v>
       </c>
       <c r="L25">
-        <v>15.59999685599541</v>
+        <v>15.59999685438015</v>
       </c>
       <c r="M25">
-        <v>65.9999893499953</v>
+        <v>65.99998937928467</v>
       </c>
       <c r="N25">
-        <v>110.9999759299935</v>
+        <v>110.9999759356506</v>
       </c>
       <c r="O25">
-        <v>165.9999732700016</v>
+        <v>165.9999733242112</v>
       </c>
       <c r="P25">
-        <v>279.99996044</v>
+        <v>279.9999605407284</v>
       </c>
       <c r="S25">
         <v>27</v>
@@ -3268,19 +3268,19 @@
         <v>16</v>
       </c>
       <c r="U25">
-        <v>-23.9999975339997</v>
+        <v>-23.99999754547389</v>
       </c>
       <c r="V25">
-        <v>-89.9999922200077</v>
+        <v>-89.99999228086381</v>
       </c>
       <c r="W25">
-        <v>-142.9999856899994</v>
+        <v>-142.9999857983312</v>
       </c>
       <c r="X25">
-        <v>-203.9999850999957</v>
+        <v>-203.9999852645488</v>
       </c>
       <c r="Y25">
-        <v>-350.9999793700044</v>
+        <v>-350.999979629305</v>
       </c>
       <c r="AB25">
         <v>27</v>
@@ -3289,19 +3289,19 @@
         <v>17</v>
       </c>
       <c r="AD25">
-        <v>-5.400002225998833</v>
+        <v>-5.400002235654028</v>
       </c>
       <c r="AE25">
-        <v>-21.9999909599992</v>
+        <v>-21.99999095707972</v>
       </c>
       <c r="AF25">
-        <v>-40.99999465000292</v>
+        <v>-40.99999465945257</v>
       </c>
       <c r="AG25">
-        <v>-54.99998869000046</v>
+        <v>-54.99998871622302</v>
       </c>
       <c r="AH25">
-        <v>-90.99998063999919</v>
+        <v>-90.99998068517924</v>
       </c>
       <c r="AK25">
         <v>27</v>
@@ -3310,19 +3310,19 @@
         <v>11</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-1.455191522836685E-11</v>
       </c>
       <c r="AN25">
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1.455191522836685E-11</v>
       </c>
       <c r="AP25">
         <v>0</v>
       </c>
       <c r="AQ25">
-        <v>-1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AT25">
         <v>27</v>
@@ -3331,7 +3331,7 @@
         <v>12</v>
       </c>
       <c r="AV25">
-        <v>-1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AW25">
         <v>-1.455191522836685E-11</v>
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="AY25">
-        <v>-1.455191522836685E-11</v>
+        <v>1.455191522836685E-11</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.455191522836685E-11</v>
       </c>
     </row>
     <row r="26" spans="1:52">
@@ -3354,19 +3354,19 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>4.537846157999411</v>
+        <v>4.53784616693838</v>
       </c>
       <c r="D26">
-        <v>16.56307013999958</v>
+        <v>16.56307016481151</v>
       </c>
       <c r="E26">
-        <v>28.12614780000013</v>
+        <v>28.12614784467951</v>
       </c>
       <c r="F26">
-        <v>38.6892198799992</v>
+        <v>38.68921993811819</v>
       </c>
       <c r="G26">
-        <v>63.63802929999974</v>
+        <v>63.63802940506957</v>
       </c>
       <c r="J26">
         <v>22</v>
@@ -3375,19 +3375,19 @@
         <v>15</v>
       </c>
       <c r="L26">
-        <v>5.107128534004005</v>
+        <v>5.107128530302361</v>
       </c>
       <c r="M26">
-        <v>19.92138367000007</v>
+        <v>19.92138366958352</v>
       </c>
       <c r="N26">
-        <v>34.38207540999974</v>
+        <v>34.38207541583506</v>
       </c>
       <c r="O26">
-        <v>51.96892627000125</v>
+        <v>51.96892628151181</v>
       </c>
       <c r="P26">
-        <v>93.91408130999844</v>
+        <v>93.91408133981896</v>
       </c>
       <c r="S26">
         <v>22</v>
@@ -3396,19 +3396,19 @@
         <v>16</v>
       </c>
       <c r="U26">
-        <v>-7.507127268000659</v>
+        <v>-7.507127267409487</v>
       </c>
       <c r="V26">
-        <v>-26.97257594000166</v>
+        <v>-26.97257595552492</v>
       </c>
       <c r="W26">
-        <v>-47.43326504000015</v>
+        <v>-47.43326508876271</v>
       </c>
       <c r="X26">
-        <v>-69.45703531999879</v>
+        <v>-69.45703538516591</v>
       </c>
       <c r="Y26">
-        <v>-125.6819152700018</v>
+        <v>-125.681915388499</v>
       </c>
       <c r="AB26">
         <v>22</v>
@@ -3417,19 +3417,19 @@
         <v>17</v>
       </c>
       <c r="AD26">
-        <v>-1.537847670000247</v>
+        <v>-1.537847667930691</v>
       </c>
       <c r="AE26">
-        <v>-6.948805290000109</v>
+        <v>-6.948805289368465</v>
       </c>
       <c r="AF26">
-        <v>-13.46069424000052</v>
+        <v>-13.46069425037103</v>
       </c>
       <c r="AG26">
-        <v>-19.40950075000092</v>
+        <v>-19.40950075910177</v>
       </c>
       <c r="AH26">
-        <v>-35.48445884000057</v>
+        <v>-35.48445885300816</v>
       </c>
       <c r="AK26">
         <v>22</v>
@@ -3444,13 +3444,13 @@
         <v>0</v>
       </c>
       <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
         <v>-3.637978807091713E-12</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>3.637978807091713E-12</v>
       </c>
       <c r="AT26">
         <v>22</v>
@@ -3462,16 +3462,16 @@
         <v>0</v>
       </c>
       <c r="AW26">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>-3.637978807091713E-12</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>3.637978807091713E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:52">
@@ -3482,19 +3482,19 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>9.000001271999281</v>
+        <v>9.000001273971066</v>
       </c>
       <c r="D27">
-        <v>30.00000050999916</v>
+        <v>30.00000051311144</v>
       </c>
       <c r="E27">
-        <v>54.99999609999941</v>
+        <v>54.99999611341809</v>
       </c>
       <c r="F27">
-        <v>78.99999735999882</v>
+        <v>78.99999738563565</v>
       </c>
       <c r="G27">
-        <v>129.9999959100005</v>
+        <v>129.999995967104</v>
       </c>
       <c r="J27">
         <v>29</v>
@@ -3503,19 +3503,19 @@
         <v>15</v>
       </c>
       <c r="L27">
-        <v>9.599994516000152</v>
+        <v>9.599994523599889</v>
       </c>
       <c r="M27">
-        <v>44.99997429999712</v>
+        <v>44.99997430574876</v>
       </c>
       <c r="N27">
-        <v>79.99995607000528</v>
+        <v>79.99995608787867</v>
       </c>
       <c r="O27">
-        <v>114.9999410000018</v>
+        <v>114.9999410141791</v>
       </c>
       <c r="P27">
-        <v>192.9998960800004</v>
+        <v>192.9998961224556</v>
       </c>
       <c r="S27">
         <v>29</v>
@@ -3524,19 +3524,19 @@
         <v>16</v>
       </c>
       <c r="U27">
-        <v>-13.79999480400329</v>
+        <v>-13.79999480801234</v>
       </c>
       <c r="V27">
-        <v>-57.99997917999645</v>
+        <v>-57.99997917538349</v>
       </c>
       <c r="W27">
-        <v>-96.99996904999716</v>
+        <v>-96.9999690848781</v>
       </c>
       <c r="X27">
-        <v>-145.9999503699983</v>
+        <v>-145.9999504107509</v>
       </c>
       <c r="Y27">
-        <v>-239.9999243300008</v>
+        <v>-239.9999244064602</v>
       </c>
       <c r="AB27">
         <v>29</v>
@@ -3545,19 +3545,19 @@
         <v>17</v>
       </c>
       <c r="AD27">
-        <v>-4.799997257999166</v>
+        <v>-4.799997257334326</v>
       </c>
       <c r="AE27">
-        <v>-17.99999241000023</v>
+        <v>-17.99999241634123</v>
       </c>
       <c r="AF27">
-        <v>-28.99998896999932</v>
+        <v>-28.99998896265333</v>
       </c>
       <c r="AG27">
-        <v>-45.99997987999996</v>
+        <v>-45.99997987836105</v>
       </c>
       <c r="AH27">
-        <v>-75.99997127999814</v>
+        <v>-75.99997129103213</v>
       </c>
       <c r="AK27">
         <v>29</v>
@@ -3610,19 +3610,19 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>1.199948933999395</v>
+        <v>1.199948936781766</v>
       </c>
       <c r="D28">
-        <v>4.99987625000017</v>
+        <v>4.999876244949746</v>
       </c>
       <c r="E28">
-        <v>4.999917959999948</v>
+        <v>4.999917947533959</v>
       </c>
       <c r="F28">
-        <v>9.999745849999726</v>
+        <v>9.999745842406355</v>
       </c>
       <c r="G28">
-        <v>14.99962391999975</v>
+        <v>14.99962388817016</v>
       </c>
       <c r="J28">
         <v>21</v>
@@ -3631,19 +3631,19 @@
         <v>15</v>
       </c>
       <c r="L28">
-        <v>2.999875991999033</v>
+        <v>2.999875990054534</v>
       </c>
       <c r="M28">
-        <v>11.99958495999999</v>
+        <v>11.99958494502152</v>
       </c>
       <c r="N28">
-        <v>16.99942774999909</v>
+        <v>16.99942773370185</v>
       </c>
       <c r="O28">
-        <v>24.99909919999936</v>
+        <v>24.99909917889363</v>
       </c>
       <c r="P28">
-        <v>38.99865036000028</v>
+        <v>38.99865031912486</v>
       </c>
       <c r="S28">
         <v>21</v>
@@ -3652,19 +3652,19 @@
         <v>16</v>
       </c>
       <c r="U28">
-        <v>-2.999926440000309</v>
+        <v>-2.999926435399175</v>
       </c>
       <c r="V28">
-        <v>-10.9996716200003</v>
+        <v>-10.99967160782398</v>
       </c>
       <c r="W28">
-        <v>-16.99946447999901</v>
+        <v>-16.99946445980913</v>
       </c>
       <c r="X28">
-        <v>-24.99921910000012</v>
+        <v>-24.99921907130738</v>
       </c>
       <c r="Y28">
-        <v>-35.99893187999987</v>
+        <v>-35.99893183357835</v>
       </c>
       <c r="AB28">
         <v>21</v>
@@ -3673,19 +3673,19 @@
         <v>17</v>
       </c>
       <c r="AD28">
-        <v>-1.199926385999788</v>
+        <v>-1.199926382050307</v>
       </c>
       <c r="AE28">
-        <v>-4.999792000000525</v>
+        <v>-4.999791993543113</v>
       </c>
       <c r="AF28">
-        <v>-6.999709309999616</v>
+        <v>-6.999709311825427</v>
       </c>
       <c r="AG28">
-        <v>-9.999670100000005</v>
+        <v>-9.999670094824069</v>
       </c>
       <c r="AH28">
-        <v>-16.99942525000006</v>
+        <v>-16.99942523477876</v>
       </c>
       <c r="AK28">
         <v>21</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>12</v>
       </c>
       <c r="AV28">
-        <v>-1.818989403545856E-12</v>
+        <v>0</v>
       </c>
       <c r="AW28">
         <v>0</v>
@@ -3724,10 +3724,10 @@
         <v>0</v>
       </c>
       <c r="AY28">
-        <v>-1.818989403545856E-12</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>1.818989403545856E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:52">
@@ -3738,19 +3738,19 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>4.200091805999818</v>
+        <v>4.200091798056292</v>
       </c>
       <c r="D29">
-        <v>11.00010096000005</v>
+        <v>11.00010097491804</v>
       </c>
       <c r="E29">
-        <v>13.00017124999931</v>
+        <v>13.00017127728643</v>
       </c>
       <c r="F29">
-        <v>25.0002712699984</v>
+        <v>25.00027129320233</v>
       </c>
       <c r="G29">
-        <v>35.0003527599988</v>
+        <v>35.00035280599695</v>
       </c>
       <c r="J29">
         <v>26</v>
@@ -3759,19 +3759,19 @@
         <v>15</v>
       </c>
       <c r="L29">
-        <v>6.60015643800034</v>
+        <v>6.600156442627849</v>
       </c>
       <c r="M29">
-        <v>31.00051774000531</v>
+        <v>31.0005177649764</v>
       </c>
       <c r="N29">
-        <v>50.00082275000023</v>
+        <v>50.00082278209265</v>
       </c>
       <c r="O29">
-        <v>76.00113983999836</v>
+        <v>76.00113988508383</v>
       </c>
       <c r="P29">
-        <v>120.0017545600022</v>
+        <v>120.0017546467388</v>
       </c>
       <c r="S29">
         <v>26</v>
@@ -3780,19 +3780,19 @@
         <v>16</v>
       </c>
       <c r="U29">
-        <v>-9.000098304004496</v>
+        <v>-9.000098308832094</v>
       </c>
       <c r="V29">
-        <v>-28.00044792000336</v>
+        <v>-28.00044794022505</v>
       </c>
       <c r="W29">
-        <v>-49.00066081000114</v>
+        <v>-49.00066084312493</v>
       </c>
       <c r="X29">
-        <v>-69.00094289000117</v>
+        <v>-69.00094295058989</v>
       </c>
       <c r="Y29">
-        <v>-108.0012998999991</v>
+        <v>-108.0012999995761</v>
       </c>
       <c r="AB29">
         <v>26</v>
@@ -3801,19 +3801,19 @@
         <v>17</v>
       </c>
       <c r="AD29">
-        <v>-1.200082086002112</v>
+        <v>-1.200082095830112</v>
       </c>
       <c r="AE29">
-        <v>-11.00026231999982</v>
+        <v>-11.00026232264918</v>
       </c>
       <c r="AF29">
-        <v>-21.0003104999987</v>
+        <v>-21.00031050470807</v>
       </c>
       <c r="AG29">
-        <v>-30.00042628999927</v>
+        <v>-30.00042629671225</v>
       </c>
       <c r="AH29">
-        <v>-49.00072234000072</v>
+        <v>-49.00072237251607</v>
       </c>
       <c r="AK29">
         <v>26</v>
@@ -3822,19 +3822,19 @@
         <v>11</v>
       </c>
       <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
         <v>-7.275957614183426E-12</v>
       </c>
-      <c r="AN29">
-        <v>0</v>
-      </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
-      <c r="AP29">
-        <v>0</v>
-      </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>-7.275957614183426E-12</v>
       </c>
       <c r="AT29">
         <v>26</v>
@@ -3866,19 +3866,19 @@
         <v>14</v>
       </c>
       <c r="C30">
-        <v>13.80000296399885</v>
+        <v>13.80000296820981</v>
       </c>
       <c r="D30">
-        <v>45.00020641000083</v>
+        <v>45.00020641069568</v>
       </c>
       <c r="E30">
-        <v>77.00018666000142</v>
+        <v>77.00018665618518</v>
       </c>
       <c r="F30">
-        <v>110.0003745800004</v>
+        <v>110.0003745842168</v>
       </c>
       <c r="G30">
-        <v>179.0006520100014</v>
+        <v>179.0006520042298</v>
       </c>
       <c r="J30">
         <v>24</v>
@@ -3887,19 +3887,19 @@
         <v>15</v>
       </c>
       <c r="L30">
-        <v>11.99996944199665</v>
+        <v>11.99996943957012</v>
       </c>
       <c r="M30">
-        <v>57.99990772000092</v>
+        <v>57.99990769708529</v>
       </c>
       <c r="N30">
-        <v>103.9997606100005</v>
+        <v>103.9997605794961</v>
       </c>
       <c r="O30">
-        <v>154.9997962099987</v>
+        <v>154.9997961812078</v>
       </c>
       <c r="P30">
-        <v>262.9997108899988</v>
+        <v>262.9997108542339</v>
       </c>
       <c r="S30">
         <v>24</v>
@@ -3908,19 +3908,19 @@
         <v>16</v>
       </c>
       <c r="U30">
-        <v>-21.00000278399967</v>
+        <v>-21.00000278104926</v>
       </c>
       <c r="V30">
-        <v>-81.9999959500019</v>
+        <v>-81.99999592763925</v>
       </c>
       <c r="W30">
-        <v>-139.0000719999989</v>
+        <v>-139.0000719815944</v>
       </c>
       <c r="X30">
-        <v>-196.000164420002</v>
+        <v>-196.0001643953983</v>
       </c>
       <c r="Y30">
-        <v>-330.0003459900036</v>
+        <v>-330.0003459416803</v>
       </c>
       <c r="AB30">
         <v>24</v>
@@ -3929,19 +3929,19 @@
         <v>17</v>
       </c>
       <c r="AD30">
-        <v>-5.400013662000674</v>
+        <v>-5.400013655867042</v>
       </c>
       <c r="AE30">
-        <v>-20.99997962999805</v>
+        <v>-20.99997963352416</v>
       </c>
       <c r="AF30">
-        <v>-41.00001621000138</v>
+        <v>-41.00001620447802</v>
       </c>
       <c r="AG30">
-        <v>-65.99999383000068</v>
+        <v>-65.99999382375245</v>
       </c>
       <c r="AH30">
-        <v>-107.000015460002</v>
+        <v>-107.0000154564714</v>
       </c>
       <c r="AK30">
         <v>24</v>
@@ -3953,13 +3953,13 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.455191522836685E-11</v>
       </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>-1.455191522836685E-11</v>
+        <v>1.455191522836685E-11</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -3994,19 +3994,19 @@
         <v>14</v>
       </c>
       <c r="C31">
-        <v>26.39995105800336</v>
+        <v>26.39995105821436</v>
       </c>
       <c r="D31">
-        <v>99.9998051099974</v>
+        <v>99.99980509529632</v>
       </c>
       <c r="E31">
-        <v>158.9997144999943</v>
+        <v>158.9997144879781</v>
       </c>
       <c r="F31">
-        <v>231.9995737800018</v>
+        <v>231.9995737495301</v>
       </c>
       <c r="G31">
-        <v>371.9993232499983</v>
+        <v>371.9993232321103</v>
       </c>
       <c r="J31">
         <v>23</v>
@@ -4015,19 +4015,19 @@
         <v>15</v>
       </c>
       <c r="L31">
-        <v>7.199994276008511</v>
+        <v>7.199994273207267</v>
       </c>
       <c r="M31">
-        <v>42.99996684000507</v>
+        <v>42.99996683432255</v>
       </c>
       <c r="N31">
-        <v>76.99994958999741</v>
+        <v>76.9999495729935</v>
       </c>
       <c r="O31">
-        <v>120.9998982000034</v>
+        <v>120.9998981616664</v>
       </c>
       <c r="P31">
-        <v>222.9997791900023</v>
+        <v>222.9997791136193</v>
       </c>
       <c r="S31">
         <v>23</v>
@@ -4036,19 +4036,19 @@
         <v>16</v>
       </c>
       <c r="U31">
-        <v>-26.39996433000124</v>
+        <v>-26.39996433039414</v>
       </c>
       <c r="V31">
-        <v>-107.9998588400012</v>
+        <v>-107.9998588340532</v>
       </c>
       <c r="W31">
-        <v>-184.9997478800142</v>
+        <v>-184.9997478685509</v>
       </c>
       <c r="X31">
-        <v>-274.9995990400021</v>
+        <v>-274.9995990029747</v>
       </c>
       <c r="Y31">
-        <v>-460.9993005600045</v>
+        <v>-460.9993005073157</v>
       </c>
       <c r="AB31">
         <v>23</v>
@@ -4057,19 +4057,19 @@
         <v>17</v>
       </c>
       <c r="AD31">
-        <v>-7.199979995999456</v>
+        <v>-7.199979991504733</v>
       </c>
       <c r="AE31">
-        <v>-24.99995912000123</v>
+        <v>-24.99995911337282</v>
       </c>
       <c r="AF31">
-        <v>-51.9999487999994</v>
+        <v>-51.99994878959933</v>
       </c>
       <c r="AG31">
-        <v>-78.99988742000096</v>
+        <v>-78.99988739901892</v>
       </c>
       <c r="AH31">
-        <v>-134.999793089999</v>
+        <v>-134.9997930450863</v>
       </c>
       <c r="AK31">
         <v>23</v>
@@ -4081,13 +4081,13 @@
         <v>0</v>
       </c>
       <c r="AN31">
-        <v>-1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>-1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.455191522836685E-11</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>-1.455191522836685E-11</v>
       </c>
       <c r="AY31">
         <v>0</v>
@@ -4122,19 +4122,19 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>4.200002717999723</v>
+        <v>4.200002706479609</v>
       </c>
       <c r="D32">
-        <v>15.00001034000024</v>
+        <v>15.00001027160306</v>
       </c>
       <c r="E32">
-        <v>27.00000712000019</v>
+        <v>27.00000703573687</v>
       </c>
       <c r="F32">
-        <v>35.00001844999997</v>
+        <v>35.00001833262377</v>
       </c>
       <c r="G32">
-        <v>57.00002401000029</v>
+        <v>57.00002383528954</v>
       </c>
       <c r="J32">
         <v>25</v>
@@ -4143,19 +4143,19 @@
         <v>15</v>
       </c>
       <c r="L32">
-        <v>4.200001242001235</v>
+        <v>4.200001218443504</v>
       </c>
       <c r="M32">
-        <v>16.00000888999966</v>
+        <v>16.00000877937418</v>
       </c>
       <c r="N32">
-        <v>31.00001634999717</v>
+        <v>31.00001616598274</v>
       </c>
       <c r="O32">
-        <v>47.00002372999916</v>
+        <v>47.00002345225039</v>
       </c>
       <c r="P32">
-        <v>80.00004061000254</v>
+        <v>80.00004017672109</v>
       </c>
       <c r="S32">
         <v>25</v>
@@ -4164,19 +4164,19 @@
         <v>16</v>
       </c>
       <c r="U32">
-        <v>-6.000002609999683</v>
+        <v>-6.000002579707143</v>
       </c>
       <c r="V32">
-        <v>-26.00001213000087</v>
+        <v>-26.00001201441956</v>
       </c>
       <c r="W32">
-        <v>-42.00002188000053</v>
+        <v>-42.00002169547133</v>
       </c>
       <c r="X32">
-        <v>-60.00003725000079</v>
+        <v>-60.00003697144075</v>
       </c>
       <c r="Y32">
-        <v>-99.0000589299998</v>
+        <v>-99.00005850588695</v>
       </c>
       <c r="AB32">
         <v>25</v>
@@ -4185,19 +4185,19 @@
         <v>17</v>
       </c>
       <c r="AD32">
-        <v>-1.799999802000002</v>
+        <v>-1.799999800366095</v>
       </c>
       <c r="AE32">
-        <v>-9.000000470000032</v>
+        <v>-9.000000428982275</v>
       </c>
       <c r="AF32">
-        <v>-15.0000024900005</v>
+        <v>-15.00000241274074</v>
       </c>
       <c r="AG32">
-        <v>-20.00000798000019</v>
+        <v>-20.00000786544933</v>
       </c>
       <c r="AH32">
-        <v>-35.00001616999998</v>
+        <v>-35.00001600001406</v>
       </c>
       <c r="AK32">
         <v>25</v>
@@ -4206,7 +4206,7 @@
         <v>11</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AN32">
         <v>0</v>
@@ -4215,10 +4215,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AQ32">
-        <v>-3.637978807091713E-12</v>
+        <v>3.637978807091713E-12</v>
       </c>
       <c r="AT32">
         <v>25</v>
